--- a/converted/oylik/2026-06/Elektr Fiderlar.xlsx
+++ b/converted/oylik/2026-06/Elektr Fiderlar.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="169">
   <si>
     <t>Fiderlar Iyun Holatiga Ko'ra</t>
   </si>
@@ -49,12 +49,21 @@
     <t>Umumiy oqim (7 oylik jami)</t>
   </si>
   <si>
+    <t>Umumiy oqim (fider faylida)</t>
+  </si>
+  <si>
     <t>Foydali oqim (7 oylik jami)</t>
   </si>
   <si>
+    <t>Foydali oqim (fider faylida)</t>
+  </si>
+  <si>
     <t>Yo’qotish (7 oylik jami)</t>
   </si>
   <si>
+    <t>Yo’qotish (fider faylida)</t>
+  </si>
+  <si>
     <t>Yo’qotish (manba)</t>
   </si>
   <si>
@@ -67,6 +76,9 @@
     <t>Ma'sul xodim (manba)</t>
   </si>
   <si>
+    <t>Eslatma</t>
+  </si>
+  <si>
     <t>Manba (fayl, qator)</t>
   </si>
   <si>
@@ -127,6 +139,9 @@
     <t xml:space="preserve">Ziyokor </t>
   </si>
   <si>
+    <t>Shu oyda TP oqimlari yo'q - oqim fider faylida qolgan (TP lari yig'indisi 0)</t>
+  </si>
+  <si>
     <t>baliqchi/7 oylik/Elektr Fiderlar.xlsx, 6-qator</t>
   </si>
   <si>
@@ -310,6 +325,9 @@
     <t>С.Мирзахакимов</t>
   </si>
   <si>
+    <t>Quvvati (KVA) o'rnida kuchlanish (kV) yozilgan - bo'sh qoldirildi</t>
+  </si>
+  <si>
     <t>chinobod/Elektr Fiderlar.xlsx [7 oy], 3-qator</t>
   </si>
   <si>
@@ -355,6 +373,9 @@
     <t>Фаровон МФЙ</t>
   </si>
   <si>
+    <t>Quvvati (KVA) o'rnida kuchlanish (kV) yozilgan - bo'sh qoldirildi; Shu oyda TP oqimlari yo'q - oqim fider faylida qolgan (TP lari yig'indisi 0)</t>
+  </si>
+  <si>
     <t>chinobod/Elektr Fiderlar.xlsx [7 oy], 6-qator</t>
   </si>
   <si>
@@ -452,6 +473,51 @@
   </si>
   <si>
     <t>chinobod/Elektr Fiderlar.xlsx [7 oy], 12-qator</t>
+  </si>
+  <si>
+    <t>Sevin TIM</t>
+  </si>
+  <si>
+    <t>baliqchi_transformatorlar.xlsx [Iyun], 369-qator</t>
+  </si>
+  <si>
+    <t>Oltinko'l</t>
+  </si>
+  <si>
+    <t>Alpomish</t>
+  </si>
+  <si>
+    <t>transformatorlar.xlsx [Iyun], 41-qator</t>
+  </si>
+  <si>
+    <t>Muqum</t>
+  </si>
+  <si>
+    <t>Fiderlar faylida yo'q, faqat reestr yoki quyi fayllarda bor - oqim 0</t>
+  </si>
+  <si>
+    <t>baliqchi/Elektr Abonentlar.xlsx, 6583-qator</t>
+  </si>
+  <si>
+    <t>Olimbek</t>
+  </si>
+  <si>
+    <t>baliqchi/Elektr Abonentlar.xlsx, 10175-qator</t>
+  </si>
+  <si>
+    <t>Biriktirilmagan</t>
+  </si>
+  <si>
+    <t>Vaqtinchalik "Biriktirilmagan" fider - abonentlarning joyi hali berilmagan</t>
+  </si>
+  <si>
+    <t>chinobod/Elektr Abonentlar.xlsx, 73-qator</t>
+  </si>
+  <si>
+    <t>Bo'zchi</t>
+  </si>
+  <si>
+    <t>chinobod/Elektr Abonentlar.xlsx, 118-qator</t>
   </si>
 </sst>
 </file>
@@ -866,7 +932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:V34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
@@ -874,10 +940,10 @@
     <col min="6" max="6" width="34" customWidth="1"/>
     <col min="7" max="7" width="18" style="1" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="18" width="26" customWidth="1"/>
+    <col min="9" max="22" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -898,8 +964,12 @@
       <c r="P1"/>
       <c r="Q1"/>
       <c r="R1"/>
-    </row>
-    <row r="2" ht="45" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S1"/>
+      <c r="T1"/>
+      <c r="U1"/>
+      <c r="V1"/>
+    </row>
+    <row r="2" ht="45" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -954,139 +1024,178 @@
       <c r="R2" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1">
-        <v>37467.43</v>
+        <v>520394.406272</v>
       </c>
       <c r="D3" s="1">
-        <v>33092.29</v>
+        <v>402764.16812</v>
       </c>
       <c r="E3" s="1">
-        <v>4946.43</v>
+        <v>117630.238152</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K3">
         <v>262272</v>
       </c>
       <c r="L3">
+        <v>37467.43</v>
+      </c>
+      <c r="M3">
         <v>231646</v>
       </c>
-      <c r="M3">
+      <c r="N3">
+        <v>33092.29</v>
+      </c>
+      <c r="O3">
         <v>34625</v>
       </c>
-      <c r="O3" t="s">
-        <v>25</v>
+      <c r="P3">
+        <v>4946.43</v>
       </c>
       <c r="R3" t="s">
+        <v>29</v>
+      </c>
+      <c r="V3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1">
+        <v>357959.368429</v>
+      </c>
+      <c r="D4" s="1">
+        <v>276288.094049</v>
+      </c>
+      <c r="E4" s="1">
+        <v>81671.27438</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="I4" t="s">
         <v>27</v>
-      </c>
-      <c r="C4" s="1">
-        <v>26287.71</v>
-      </c>
-      <c r="D4" s="1">
-        <v>23014.57</v>
-      </c>
-      <c r="E4" s="1">
-        <v>3273.14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" t="s">
-        <v>23</v>
       </c>
       <c r="K4">
         <v>184014</v>
       </c>
       <c r="L4">
+        <v>26287.71</v>
+      </c>
+      <c r="M4">
         <v>161102</v>
       </c>
-      <c r="M4">
+      <c r="N4">
+        <v>23014.57</v>
+      </c>
+      <c r="O4">
         <v>22912</v>
       </c>
-      <c r="O4" t="s">
-        <v>29</v>
+      <c r="P4">
+        <v>3273.14</v>
       </c>
       <c r="R4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="V4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C5" s="1">
-        <v>36837.14</v>
+        <v>631822.609408</v>
       </c>
       <c r="D5" s="1">
-        <v>31374</v>
+        <v>469074.122679</v>
       </c>
       <c r="E5" s="1">
-        <v>5463</v>
+        <v>162748.486728</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K5">
         <v>257860</v>
       </c>
       <c r="L5">
+        <v>36837.14</v>
+      </c>
+      <c r="M5">
         <v>219618</v>
       </c>
-      <c r="M5">
+      <c r="N5">
+        <v>31374</v>
+      </c>
+      <c r="O5">
         <v>38241</v>
       </c>
-      <c r="O5" t="s">
-        <v>33</v>
+      <c r="P5">
+        <v>5463</v>
       </c>
       <c r="R5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="V5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1">
         <v>439.35</v>
@@ -1098,36 +1207,39 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K6">
         <v>3075.46</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>3075.46</v>
       </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>37</v>
+      <c r="O6">
+        <v>0</v>
       </c>
       <c r="R6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="U6" t="s">
+        <v>42</v>
+      </c>
+      <c r="V6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C7" s="1">
         <v>49.27</v>
@@ -1139,36 +1251,39 @@
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K7">
         <v>344.91</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>344.91</v>
       </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>19</v>
+      <c r="O7">
+        <v>0</v>
       </c>
       <c r="R7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="U7" t="s">
+        <v>42</v>
+      </c>
+      <c r="V7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C8" s="1">
         <v>0</v>
@@ -1180,130 +1295,148 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="R8" t="s">
         <v>23</v>
       </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>19</v>
-      </c>
-      <c r="R8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="V8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C9" s="1">
-        <v>0</v>
+        <v>9588.792549</v>
       </c>
       <c r="D9" s="1">
-        <v>0</v>
+        <v>6396.300582</v>
       </c>
       <c r="E9" s="1">
-        <v>0</v>
+        <v>3192.491967</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H9" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>55</v>
+      </c>
+      <c r="T9" t="s">
+        <v>56</v>
+      </c>
+      <c r="V9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>49</v>
       </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q9" t="s">
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="1">
+        <v>71008.792549</v>
+      </c>
+      <c r="D10" s="1">
+        <v>67816.300582</v>
+      </c>
+      <c r="E10" s="1">
+        <v>3192.491967</v>
+      </c>
+      <c r="F10" t="s">
         <v>51</v>
       </c>
-      <c r="R9" t="s">
+      <c r="H10" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="I10" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="1">
-        <v>528.57</v>
-      </c>
-      <c r="D10" s="1">
-        <v>528.57</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0</v>
-      </c>
-      <c r="F10" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" t="s">
-        <v>48</v>
-      </c>
       <c r="J10" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K10">
         <v>3700</v>
       </c>
       <c r="L10">
+        <v>528.57</v>
+      </c>
+      <c r="M10">
         <v>3700</v>
       </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>50</v>
+      <c r="N10">
+        <v>528.57</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
       </c>
       <c r="Q10" t="s">
-        <v>51</v>
-      </c>
-      <c r="R10" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="T10" t="s">
+        <v>56</v>
+      </c>
+      <c r="V10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C11" s="1">
         <v>1594.29</v>
@@ -1315,324 +1448,381 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H11" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J11" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K11">
         <v>11160</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>11160</v>
       </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>50</v>
+      <c r="O11">
+        <v>0</v>
       </c>
       <c r="Q11" t="s">
+        <v>55</v>
+      </c>
+      <c r="T11" t="s">
+        <v>56</v>
+      </c>
+      <c r="U11" t="s">
+        <v>42</v>
+      </c>
+      <c r="V11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="1">
+        <v>9588.792549</v>
+      </c>
+      <c r="D12" s="1">
+        <v>6396.300582</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3192.491967</v>
+      </c>
+      <c r="F12" t="s">
         <v>51</v>
       </c>
-      <c r="R11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="1">
-        <v>991.43</v>
-      </c>
-      <c r="D12" s="1">
-        <v>991.43</v>
-      </c>
-      <c r="E12" s="1">
-        <v>0</v>
-      </c>
-      <c r="F12" t="s">
-        <v>46</v>
-      </c>
       <c r="H12" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I12" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J12" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K12">
         <v>6940</v>
       </c>
       <c r="L12">
+        <v>991.43</v>
+      </c>
+      <c r="M12">
         <v>6940</v>
       </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>50</v>
+      <c r="N12">
+        <v>991.43</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>51</v>
-      </c>
-      <c r="R12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="T12" t="s">
+        <v>56</v>
+      </c>
+      <c r="V12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C13" s="1">
-        <v>2270.87</v>
+        <v>895429.671565</v>
       </c>
       <c r="D13" s="1">
-        <v>1723.09</v>
+        <v>724271.521609</v>
       </c>
       <c r="E13" s="1">
-        <v>547.78</v>
+        <v>171158.149957</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H13" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J13" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="K13">
         <v>15896.078</v>
       </c>
       <c r="L13">
+        <v>2270.87</v>
+      </c>
+      <c r="M13">
         <v>12061.601</v>
       </c>
-      <c r="M13">
+      <c r="N13">
+        <v>1723.09</v>
+      </c>
+      <c r="O13">
         <v>3834.476999999999</v>
       </c>
-      <c r="O13" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>51</v>
+      <c r="P13">
+        <v>547.78</v>
       </c>
       <c r="R13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="T13" t="s">
+        <v>56</v>
+      </c>
+      <c r="V13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C14" s="1">
-        <v>3214.94</v>
+        <v>1645247.576071</v>
       </c>
       <c r="D14" s="1">
-        <v>2846.17</v>
+        <v>1276333.594451</v>
       </c>
       <c r="E14" s="1">
-        <v>368.77</v>
+        <v>368913.98162</v>
       </c>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H14" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J14" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="K14">
         <v>22504.562</v>
       </c>
       <c r="L14">
+        <v>3214.94</v>
+      </c>
+      <c r="M14">
         <v>19923.183</v>
       </c>
-      <c r="M14">
+      <c r="N14">
+        <v>2846.17</v>
+      </c>
+      <c r="O14">
         <v>2581.379000000001</v>
       </c>
-      <c r="O14" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>51</v>
+      <c r="P14">
+        <v>368.77</v>
       </c>
       <c r="R14" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="T14" t="s">
+        <v>56</v>
+      </c>
+      <c r="V14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C15" s="1">
-        <v>2327.29</v>
+        <v>537234.99019</v>
       </c>
       <c r="D15" s="1">
-        <v>2080.68</v>
+        <v>352942.811984</v>
       </c>
       <c r="E15" s="1">
-        <v>246.61</v>
+        <v>184292.178207</v>
       </c>
       <c r="F15" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I15" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J15" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K15">
         <v>16291.03</v>
       </c>
       <c r="L15">
+        <v>2327.29</v>
+      </c>
+      <c r="M15">
         <v>14564.79</v>
       </c>
-      <c r="M15">
+      <c r="N15">
+        <v>2080.68</v>
+      </c>
+      <c r="O15">
         <v>1726.2399999999998</v>
       </c>
-      <c r="O15" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>51</v>
+      <c r="P15">
+        <v>246.61</v>
       </c>
       <c r="R15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="T15" t="s">
+        <v>56</v>
+      </c>
+      <c r="V15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C16" s="1">
-        <v>4631.72</v>
+        <v>1989549.185326</v>
       </c>
       <c r="D16" s="1">
-        <v>4418.19</v>
+        <v>1636992.029543</v>
       </c>
       <c r="E16" s="1">
-        <v>213.52</v>
+        <v>352557.155783</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H16" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I16" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J16" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K16">
         <v>32422.007</v>
       </c>
       <c r="L16">
+        <v>4631.72</v>
+      </c>
+      <c r="M16">
         <v>30927.341</v>
       </c>
-      <c r="M16">
+      <c r="N16">
+        <v>4418.19</v>
+      </c>
+      <c r="O16">
         <v>1494.666000000001</v>
       </c>
-      <c r="O16" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>51</v>
+      <c r="P16">
+        <v>213.52</v>
       </c>
       <c r="R16" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="T16" t="s">
+        <v>56</v>
+      </c>
+      <c r="V16" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C17" s="1">
-        <v>4742.78</v>
+        <v>1855932.022543</v>
       </c>
       <c r="D17" s="1">
-        <v>4035.76</v>
+        <v>1559171.455239</v>
       </c>
       <c r="E17" s="1">
-        <v>707.01</v>
+        <v>296760.567304</v>
       </c>
       <c r="F17" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I17" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J17" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="K17">
         <v>33199.432</v>
       </c>
       <c r="L17">
+        <v>4742.78</v>
+      </c>
+      <c r="M17">
         <v>28250.33</v>
       </c>
-      <c r="M17">
+      <c r="N17">
+        <v>4035.76</v>
+      </c>
+      <c r="O17">
         <v>4949.101999999999</v>
       </c>
-      <c r="O17" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>51</v>
+      <c r="P17">
+        <v>707.01</v>
       </c>
       <c r="R17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="T17" t="s">
+        <v>56</v>
+      </c>
+      <c r="V17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C18" s="1">
         <v>229.19</v>
@@ -1644,189 +1834,228 @@
         <v>65.79</v>
       </c>
       <c r="F18" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H18" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I18" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J18" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="K18">
         <v>1604.3</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>1143.74</v>
       </c>
-      <c r="M18">
+      <c r="O18">
         <v>460.55999999999995</v>
       </c>
-      <c r="Q18" t="s">
-        <v>51</v>
-      </c>
-      <c r="R18" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="T18" t="s">
+        <v>56</v>
+      </c>
+      <c r="U18" t="s">
+        <v>42</v>
+      </c>
+      <c r="V18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C19" s="1">
-        <v>272000</v>
+        <v>268180.863537</v>
       </c>
       <c r="D19" s="1">
-        <v>228480</v>
+        <v>224787.376324</v>
       </c>
       <c r="E19" s="1">
-        <v>43520</v>
+        <v>43393.487213</v>
       </c>
       <c r="F19" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="H19" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I19" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J19" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="K19">
         <v>1904000</v>
       </c>
       <c r="L19">
+        <v>272000</v>
+      </c>
+      <c r="M19">
         <v>1599360</v>
       </c>
-      <c r="M19">
+      <c r="N19">
+        <v>228480</v>
+      </c>
+      <c r="O19">
         <v>304640</v>
       </c>
-      <c r="O19" t="s">
-        <v>96</v>
-      </c>
-      <c r="P19" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q19" t="s">
+      <c r="P19">
+        <v>43520</v>
+      </c>
+      <c r="R19" t="s">
+        <v>101</v>
+      </c>
+      <c r="S19" t="s">
+        <v>102</v>
+      </c>
+      <c r="T19" t="s">
+        <v>103</v>
+      </c>
+      <c r="U19" t="s">
+        <v>104</v>
+      </c>
+      <c r="V19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="1">
+        <v>943154.600748</v>
+      </c>
+      <c r="D20" s="1">
+        <v>788818.747462</v>
+      </c>
+      <c r="E20" s="1">
+        <v>154335.853286</v>
+      </c>
+      <c r="F20" t="s">
+        <v>107</v>
+      </c>
+      <c r="H20" t="s">
         <v>98</v>
       </c>
-      <c r="R19" t="s">
+      <c r="I20" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" t="s">
-        <v>100</v>
-      </c>
-      <c r="C20" s="1">
-        <v>629714.29</v>
-      </c>
-      <c r="D20" s="1">
-        <v>528960</v>
-      </c>
-      <c r="E20" s="1">
-        <v>100754.29</v>
-      </c>
-      <c r="F20" t="s">
-        <v>101</v>
-      </c>
-      <c r="H20" t="s">
-        <v>93</v>
-      </c>
-      <c r="I20" t="s">
-        <v>94</v>
-      </c>
       <c r="J20" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="K20">
         <v>4408000</v>
       </c>
       <c r="L20">
+        <v>629714.29</v>
+      </c>
+      <c r="M20">
         <v>3702720</v>
       </c>
-      <c r="M20">
+      <c r="N20">
+        <v>528960</v>
+      </c>
+      <c r="O20">
         <v>705280</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20">
+        <v>100754.29</v>
+      </c>
+      <c r="R20" t="s">
+        <v>109</v>
+      </c>
+      <c r="S20" t="s">
+        <v>102</v>
+      </c>
+      <c r="T20" t="s">
         <v>103</v>
       </c>
-      <c r="P20" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q20" t="s">
+      <c r="U20" t="s">
+        <v>104</v>
+      </c>
+      <c r="V20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="1">
+        <v>960894.363145</v>
+      </c>
+      <c r="D21" s="1">
+        <v>810395.496774</v>
+      </c>
+      <c r="E21" s="1">
+        <v>150498.866371</v>
+      </c>
+      <c r="F21" t="s">
+        <v>112</v>
+      </c>
+      <c r="H21" t="s">
         <v>98</v>
       </c>
-      <c r="R20" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>90</v>
-      </c>
-      <c r="B21" t="s">
-        <v>105</v>
-      </c>
-      <c r="C21" s="1">
-        <v>1600285.71</v>
-      </c>
-      <c r="D21" s="1">
-        <v>1344240</v>
-      </c>
-      <c r="E21" s="1">
-        <v>256045.71</v>
-      </c>
-      <c r="F21" t="s">
-        <v>106</v>
-      </c>
-      <c r="H21" t="s">
-        <v>93</v>
-      </c>
       <c r="I21" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J21" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K21">
         <v>11202000</v>
       </c>
       <c r="L21">
+        <v>1600285.71</v>
+      </c>
+      <c r="M21">
         <v>9409680</v>
       </c>
-      <c r="M21">
+      <c r="N21">
+        <v>1344240</v>
+      </c>
+      <c r="O21">
         <v>1792320</v>
       </c>
-      <c r="O21" t="s">
-        <v>108</v>
-      </c>
-      <c r="P21" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>98</v>
+      <c r="P21">
+        <v>256045.71</v>
       </c>
       <c r="R21" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="S21" t="s">
+        <v>102</v>
+      </c>
+      <c r="T21" t="s">
+        <v>103</v>
+      </c>
+      <c r="U21" t="s">
+        <v>104</v>
+      </c>
+      <c r="V21" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C22" s="1">
         <v>238285.71</v>
@@ -1838,145 +2067,172 @@
         <v>38125.71</v>
       </c>
       <c r="F22" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H22" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I22" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J22" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K22">
         <v>1668000</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>1401120</v>
       </c>
-      <c r="M22">
+      <c r="O22">
         <v>266880</v>
       </c>
-      <c r="O22" t="s">
-        <v>113</v>
-      </c>
-      <c r="P22" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q22" t="s">
+      <c r="R22" t="s">
+        <v>119</v>
+      </c>
+      <c r="S22" t="s">
+        <v>102</v>
+      </c>
+      <c r="T22" t="s">
+        <v>103</v>
+      </c>
+      <c r="U22" t="s">
+        <v>120</v>
+      </c>
+      <c r="V22" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23" s="1">
+        <v>340675.161515</v>
+      </c>
+      <c r="D23" s="1">
+        <v>285183.665462</v>
+      </c>
+      <c r="E23" s="1">
+        <v>55491.496052</v>
+      </c>
+      <c r="F23" t="s">
+        <v>123</v>
+      </c>
+      <c r="H23" t="s">
         <v>98</v>
       </c>
-      <c r="R22" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>90</v>
-      </c>
-      <c r="B23" t="s">
-        <v>115</v>
-      </c>
-      <c r="C23" s="1">
-        <v>242142.86</v>
-      </c>
-      <c r="D23" s="1">
-        <v>203400</v>
-      </c>
-      <c r="E23" s="1">
-        <v>38742.86</v>
-      </c>
-      <c r="F23" t="s">
-        <v>116</v>
-      </c>
-      <c r="H23" t="s">
-        <v>93</v>
-      </c>
       <c r="I23" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J23" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="K23">
         <v>1695000</v>
       </c>
       <c r="L23">
+        <v>242142.86</v>
+      </c>
+      <c r="M23">
         <v>1423800</v>
       </c>
-      <c r="M23">
+      <c r="N23">
+        <v>203400</v>
+      </c>
+      <c r="O23">
         <v>271200</v>
       </c>
-      <c r="O23" t="s">
-        <v>118</v>
-      </c>
-      <c r="P23" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q23" t="s">
+      <c r="P23">
+        <v>38742.86</v>
+      </c>
+      <c r="R23" t="s">
+        <v>125</v>
+      </c>
+      <c r="S23" t="s">
+        <v>102</v>
+      </c>
+      <c r="T23" t="s">
+        <v>103</v>
+      </c>
+      <c r="U23" t="s">
+        <v>104</v>
+      </c>
+      <c r="V23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" s="1">
+        <v>635550.711555</v>
+      </c>
+      <c r="D24" s="1">
+        <v>530297.679591</v>
+      </c>
+      <c r="E24" s="1">
+        <v>105253.031964</v>
+      </c>
+      <c r="F24" t="s">
+        <v>128</v>
+      </c>
+      <c r="H24" t="s">
         <v>98</v>
       </c>
-      <c r="R23" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>90</v>
-      </c>
-      <c r="B24" t="s">
-        <v>120</v>
-      </c>
-      <c r="C24" s="1">
-        <v>591857.14</v>
-      </c>
-      <c r="D24" s="1">
-        <v>497160</v>
-      </c>
-      <c r="E24" s="1">
-        <v>94697.14</v>
-      </c>
-      <c r="F24" t="s">
-        <v>121</v>
-      </c>
-      <c r="H24" t="s">
-        <v>93</v>
-      </c>
       <c r="I24" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J24" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="K24">
         <v>4143000</v>
       </c>
       <c r="L24">
+        <v>591857.14</v>
+      </c>
+      <c r="M24">
         <v>3480120</v>
       </c>
-      <c r="M24">
+      <c r="N24">
+        <v>497160</v>
+      </c>
+      <c r="O24">
         <v>662880</v>
       </c>
-      <c r="O24" t="s">
-        <v>123</v>
-      </c>
-      <c r="P24" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>98</v>
+      <c r="P24">
+        <v>94697.14</v>
       </c>
       <c r="R24" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+      <c r="S24" t="s">
+        <v>102</v>
+      </c>
+      <c r="T24" t="s">
+        <v>103</v>
+      </c>
+      <c r="U24" t="s">
+        <v>104</v>
+      </c>
+      <c r="V24" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B25" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C25" s="1">
         <v>190571.43</v>
@@ -1988,192 +2244,381 @@
         <v>30491.43</v>
       </c>
       <c r="F25" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H25" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I25" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J25" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K25">
         <v>1334000</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>1120560</v>
       </c>
-      <c r="M25">
+      <c r="O25">
         <v>213440</v>
       </c>
-      <c r="O25" t="s">
-        <v>128</v>
-      </c>
-      <c r="P25" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q25" t="s">
+      <c r="R25" t="s">
+        <v>135</v>
+      </c>
+      <c r="S25" t="s">
+        <v>102</v>
+      </c>
+      <c r="T25" t="s">
+        <v>103</v>
+      </c>
+      <c r="U25" t="s">
+        <v>120</v>
+      </c>
+      <c r="V25" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" s="1">
+        <v>812911.08589</v>
+      </c>
+      <c r="D26" s="1">
+        <v>677141.064537</v>
+      </c>
+      <c r="E26" s="1">
+        <v>135770.021353</v>
+      </c>
+      <c r="F26" t="s">
+        <v>139</v>
+      </c>
+      <c r="H26" t="s">
         <v>98</v>
       </c>
-      <c r="R25" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>130</v>
-      </c>
-      <c r="B26" t="s">
-        <v>131</v>
-      </c>
-      <c r="C26" s="1">
-        <v>654428.57</v>
-      </c>
-      <c r="D26" s="1">
-        <v>549720</v>
-      </c>
-      <c r="E26" s="1">
-        <v>104708.57</v>
-      </c>
-      <c r="F26" t="s">
-        <v>132</v>
-      </c>
-      <c r="H26" t="s">
-        <v>93</v>
-      </c>
       <c r="I26" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="J26" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="K26">
         <v>4581000</v>
       </c>
       <c r="L26">
+        <v>654428.57</v>
+      </c>
+      <c r="M26">
         <v>3848040</v>
       </c>
-      <c r="M26">
+      <c r="N26">
+        <v>549720</v>
+      </c>
+      <c r="O26">
         <v>732960</v>
       </c>
-      <c r="O26" t="s">
-        <v>135</v>
-      </c>
-      <c r="P26" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q26" t="s">
+      <c r="P26">
+        <v>104708.57</v>
+      </c>
+      <c r="R26" t="s">
+        <v>142</v>
+      </c>
+      <c r="S26" t="s">
+        <v>102</v>
+      </c>
+      <c r="T26" t="s">
+        <v>103</v>
+      </c>
+      <c r="U26" t="s">
+        <v>104</v>
+      </c>
+      <c r="V26" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B27" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" s="1">
+        <v>628201.987072</v>
+      </c>
+      <c r="D27" s="1">
+        <v>523111.299677</v>
+      </c>
+      <c r="E27" s="1">
+        <v>105090.687395</v>
+      </c>
+      <c r="F27" t="s">
+        <v>145</v>
+      </c>
+      <c r="H27" t="s">
         <v>98</v>
       </c>
-      <c r="R26" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>130</v>
-      </c>
-      <c r="B27" t="s">
-        <v>137</v>
-      </c>
-      <c r="C27" s="1">
-        <v>1304571.43</v>
-      </c>
-      <c r="D27" s="1">
-        <v>1095840</v>
-      </c>
-      <c r="E27" s="1">
-        <v>208731.43</v>
-      </c>
-      <c r="F27" t="s">
-        <v>138</v>
-      </c>
-      <c r="H27" t="s">
-        <v>93</v>
-      </c>
       <c r="I27" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="J27" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="K27">
         <v>9132000</v>
       </c>
       <c r="L27">
+        <v>1304571.43</v>
+      </c>
+      <c r="M27">
         <v>7670880</v>
       </c>
-      <c r="M27">
+      <c r="N27">
+        <v>1095840</v>
+      </c>
+      <c r="O27">
         <v>1461120</v>
       </c>
-      <c r="O27" t="s">
+      <c r="P27">
+        <v>208731.43</v>
+      </c>
+      <c r="R27" t="s">
+        <v>147</v>
+      </c>
+      <c r="S27" t="s">
+        <v>102</v>
+      </c>
+      <c r="T27" t="s">
+        <v>103</v>
+      </c>
+      <c r="U27" t="s">
+        <v>104</v>
+      </c>
+      <c r="V27" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" s="1">
+        <v>717280.684677</v>
+      </c>
+      <c r="D28" s="1">
+        <v>598017.219688</v>
+      </c>
+      <c r="E28" s="1">
+        <v>119263.464989</v>
+      </c>
+      <c r="F28" t="s">
+        <v>150</v>
+      </c>
+      <c r="H28" t="s">
+        <v>98</v>
+      </c>
+      <c r="I28" t="s">
         <v>140</v>
       </c>
-      <c r="P27" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>98</v>
-      </c>
-      <c r="R27" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>130</v>
-      </c>
-      <c r="B28" t="s">
-        <v>142</v>
-      </c>
-      <c r="C28" s="1">
-        <v>669857.14</v>
-      </c>
-      <c r="D28" s="1">
-        <v>562680</v>
-      </c>
-      <c r="E28" s="1">
-        <v>107177.14</v>
-      </c>
-      <c r="F28" t="s">
-        <v>143</v>
-      </c>
-      <c r="H28" t="s">
-        <v>93</v>
-      </c>
-      <c r="I28" t="s">
-        <v>133</v>
-      </c>
       <c r="J28" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="K28">
         <v>4689000</v>
       </c>
       <c r="L28">
+        <v>669857.14</v>
+      </c>
+      <c r="M28">
         <v>3938760</v>
       </c>
-      <c r="M28">
+      <c r="N28">
+        <v>562680</v>
+      </c>
+      <c r="O28">
         <v>750240</v>
       </c>
-      <c r="O28" t="s">
-        <v>145</v>
-      </c>
-      <c r="P28" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>98</v>
+      <c r="P28">
+        <v>107177.14</v>
       </c>
       <c r="R28" t="s">
-        <v>146</v>
+        <v>152</v>
+      </c>
+      <c r="S28" t="s">
+        <v>102</v>
+      </c>
+      <c r="T28" t="s">
+        <v>103</v>
+      </c>
+      <c r="U28" t="s">
+        <v>104</v>
+      </c>
+      <c r="V28" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" t="s">
+        <v>154</v>
+      </c>
+      <c r="C29" s="1">
+        <v>9588.792549</v>
+      </c>
+      <c r="D29" s="1">
+        <v>6396.300582</v>
+      </c>
+      <c r="E29" s="1">
+        <v>3192.491967</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="V29" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>156</v>
+      </c>
+      <c r="B30" t="s">
+        <v>157</v>
+      </c>
+      <c r="C30" s="1">
+        <v>470067.541861</v>
+      </c>
+      <c r="D30" s="1">
+        <v>392331.450484</v>
+      </c>
+      <c r="E30" s="1">
+        <v>77736.091377</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="V30" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0</v>
+      </c>
+      <c r="U31" t="s">
+        <v>160</v>
+      </c>
+      <c r="V31" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" s="1">
+        <v>0</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
+      <c r="U32" t="s">
+        <v>160</v>
+      </c>
+      <c r="V32" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="1">
+        <v>0</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0</v>
+      </c>
+      <c r="U33" t="s">
+        <v>165</v>
+      </c>
+      <c r="V33" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" t="s">
+        <v>167</v>
+      </c>
+      <c r="C34" s="1">
+        <v>0</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0</v>
+      </c>
+      <c r="U34" t="s">
+        <v>160</v>
+      </c>
+      <c r="V34" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A1:V1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
